--- a/ket_qua_SAT.xlsx
+++ b/ket_qua_SAT.xlsx
@@ -10,7 +10,7 @@
     <sheet name="SAT Benchmark" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SAT Benchmark'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SAT Benchmark'!$A$1:$G$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,7 @@
         <v>48</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.002274</v>
+        <v>0.006541</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>4</v>
@@ -536,7 +536,7 @@
         <v>74</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.002468</v>
+        <v>0.00048</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>4</v>
@@ -563,7 +563,7 @@
         <v>105</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.000595</v>
+        <v>0.000792</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>4</v>
@@ -590,7 +590,7 @@
         <v>126</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.000562</v>
+        <v>0.000732</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>4</v>
@@ -617,7 +617,7 @@
         <v>147</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.000615</v>
+        <v>0.000781</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>4</v>
@@ -644,7 +644,7 @@
         <v>168</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.004443</v>
+        <v>0.000827</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>4</v>
@@ -671,7 +671,7 @@
         <v>189</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.00134</v>
+        <v>0.005563</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>4</v>
@@ -698,7 +698,7 @@
         <v>210</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.003809</v>
+        <v>0.001938</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>4</v>
@@ -712,20 +712,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>K_3</t>
+          <t>C_11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>48</v>
+        <v>231</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.000231</v>
+        <v>0.001184</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>4</v>
@@ -739,23 +739,23 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>K_4</t>
+          <t>C_12</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>134</v>
+        <v>252</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.002474</v>
+        <v>0.001629</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -766,23 +766,23 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>K_5</t>
+          <t>C_13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.00606</v>
+        <v>0.002336</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -793,23 +793,23 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>K_6</t>
+          <t>C_14</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>519</v>
+        <v>294</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.013195</v>
+        <v>0.002206</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -820,23 +820,23 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>K_7</t>
+          <t>C_15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>854</v>
+        <v>315</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.030069</v>
+        <v>0.001424</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Q_2</t>
+          <t>C_16</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>74</v>
+        <v>336</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.000323</v>
+        <v>0.002501</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>4</v>
@@ -874,23 +874,23 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Q_3</t>
+          <t>C_17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.002037</v>
+        <v>0.006933</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -901,32 +901,1274 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>C_18</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.005822</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>C_19</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.002168</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>C_20</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.002016</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>C_21</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0.014864</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>C_22</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0.002034</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C_23</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0.009457999999999999</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>C_24</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0.002182</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C_25</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0.003104</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>C_26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>546</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0.010737</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C_27</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0.002864</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>C_28</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0.009341</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>C_29</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0.008768</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>C_30</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>630</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0.002707</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>C_31</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>651</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0.002924</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>C_32</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>672</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0.008283</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>C_33</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>693</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.006812</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>C_34</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>714</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0.003621</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>C_35</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>735</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.003215</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>C_36</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>756</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0.003635</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>C_37</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>777</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0.003941</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>C_38</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0.012962</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>C_39</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.004573</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>C_40</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>840</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0.008064</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>C_41</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.003647</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>C_42</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0.005885</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>C_43</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>903</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0.004166</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>C_44</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>924</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0.004163</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>C_45</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>945</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0.003849</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>C_46</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>966</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0.004501</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>C_47</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>987</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0.004234</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>C_48</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0.007557</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>C_49</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1029</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0.004411</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>C_50</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0.004458</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>K_3</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0.000306</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>K_4</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>0.001021</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>K_5</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0.007454</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>K_6</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>0.016422</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>K_7</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>854</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>0.05328</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>K_8</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0.144797</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>K_9</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1899</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0.508595</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>K_10</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2645</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1.450178</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>K_11</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>3564</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>5.375454</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>K_12</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>4674</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>16.074397</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Q_2</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>0.000435</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Q_3</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>0.008296</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>Q_4</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B62" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C62" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D62" s="2" t="n">
         <v>1184</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>0.011713</v>
-      </c>
-      <c r="F17" s="2" t="n">
+      <c r="E62" s="2" t="n">
+        <v>0.020621</v>
+      </c>
+      <c r="F62" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Q_5</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>3664</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>0.140989</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>OPT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>